--- a/tool/package-generator/clients/地域共催.xlsx
+++ b/tool/package-generator/clients/地域共催.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\package-generator\clients\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60CBF5F0-832D-41A5-8A7E-8DF3FFA75391}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B2BDA19-3DA3-4BFA-A72C-995313AED946}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="6120" windowWidth="23040" windowHeight="6120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="テンプレート" sheetId="1" r:id="rId1"/>

--- a/tool/package-generator/clients/地域共催.xlsx
+++ b/tool/package-generator/clients/地域共催.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\package-generator\clients\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B2BDA19-3DA3-4BFA-A72C-995313AED946}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B75527E-0AD8-42CE-942B-75BD3716D571}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="6120" windowWidth="23040" windowHeight="6120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -661,26 +661,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9a016a34-9640-43fb-86ea-5daabefdfe7e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="2d3c347e-deae-4f57-8eaf-3772dd4433c8" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101003F084FCF046B4A45A11E77E3180ECC70" ma:contentTypeVersion="11" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="93b3c00843758588d82b9b1cc445674f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9a016a34-9640-43fb-86ea-5daabefdfe7e" xmlns:ns3="2d3c347e-deae-4f57-8eaf-3772dd4433c8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3ba47e2a8c0ba124aa1c5a854c46141a" ns2:_="" ns3:_="">
     <xsd:import namespace="9a016a34-9640-43fb-86ea-5daabefdfe7e"/>
@@ -875,26 +855,27 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9a016a34-9640-43fb-86ea-5daabefdfe7e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="2d3c347e-deae-4f57-8eaf-3772dd4433c8" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26368CF4-F3C0-43C6-B5BF-C4E959C1D0AC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D39C44C-96D4-4F11-B752-6A8BD1FE27AD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="9a016a34-9640-43fb-86ea-5daabefdfe7e"/>
-    <ds:schemaRef ds:uri="2d3c347e-deae-4f57-8eaf-3772dd4433c8"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F143D2EB-8BE1-46FD-AA36-F0A52D61EC19}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -911,4 +892,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D39C44C-96D4-4F11-B752-6A8BD1FE27AD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9a016a34-9640-43fb-86ea-5daabefdfe7e"/>
+    <ds:schemaRef ds:uri="2d3c347e-deae-4f57-8eaf-3772dd4433c8"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26368CF4-F3C0-43C6-B5BF-C4E959C1D0AC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/tool/package-generator/clients/地域共催.xlsx
+++ b/tool/package-generator/clients/地域共催.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\package-generator\clients\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B75527E-0AD8-42CE-942B-75BD3716D571}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9B19928-5F7A-4A62-9F95-53C9F6EBC187}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="6120" windowWidth="23040" windowHeight="6120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -661,6 +661,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9a016a34-9640-43fb-86ea-5daabefdfe7e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="2d3c347e-deae-4f57-8eaf-3772dd4433c8" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101003F084FCF046B4A45A11E77E3180ECC70" ma:contentTypeVersion="11" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="93b3c00843758588d82b9b1cc445674f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9a016a34-9640-43fb-86ea-5daabefdfe7e" xmlns:ns3="2d3c347e-deae-4f57-8eaf-3772dd4433c8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3ba47e2a8c0ba124aa1c5a854c46141a" ns2:_="" ns3:_="">
     <xsd:import namespace="9a016a34-9640-43fb-86ea-5daabefdfe7e"/>
@@ -855,27 +875,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9a016a34-9640-43fb-86ea-5daabefdfe7e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="2d3c347e-deae-4f57-8eaf-3772dd4433c8" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26368CF4-F3C0-43C6-B5BF-C4E959C1D0AC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D39C44C-96D4-4F11-B752-6A8BD1FE27AD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9a016a34-9640-43fb-86ea-5daabefdfe7e"/>
+    <ds:schemaRef ds:uri="2d3c347e-deae-4f57-8eaf-3772dd4433c8"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F143D2EB-8BE1-46FD-AA36-F0A52D61EC19}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -892,23 +911,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D39C44C-96D4-4F11-B752-6A8BD1FE27AD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="9a016a34-9640-43fb-86ea-5daabefdfe7e"/>
-    <ds:schemaRef ds:uri="2d3c347e-deae-4f57-8eaf-3772dd4433c8"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26368CF4-F3C0-43C6-B5BF-C4E959C1D0AC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/tool/package-generator/clients/地域共催.xlsx
+++ b/tool/package-generator/clients/地域共催.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\package-generator\clients\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9B19928-5F7A-4A62-9F95-53C9F6EBC187}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F22922CC-DCE5-4136-AE24-F7DE664A08A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="6120" windowWidth="23040" windowHeight="6120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="テンプレート" sheetId="1" r:id="rId1"/>
@@ -661,26 +661,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9a016a34-9640-43fb-86ea-5daabefdfe7e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="2d3c347e-deae-4f57-8eaf-3772dd4433c8" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101003F084FCF046B4A45A11E77E3180ECC70" ma:contentTypeVersion="11" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="93b3c00843758588d82b9b1cc445674f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9a016a34-9640-43fb-86ea-5daabefdfe7e" xmlns:ns3="2d3c347e-deae-4f57-8eaf-3772dd4433c8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3ba47e2a8c0ba124aa1c5a854c46141a" ns2:_="" ns3:_="">
     <xsd:import namespace="9a016a34-9640-43fb-86ea-5daabefdfe7e"/>
@@ -875,26 +855,27 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9a016a34-9640-43fb-86ea-5daabefdfe7e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="2d3c347e-deae-4f57-8eaf-3772dd4433c8" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26368CF4-F3C0-43C6-B5BF-C4E959C1D0AC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D39C44C-96D4-4F11-B752-6A8BD1FE27AD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="9a016a34-9640-43fb-86ea-5daabefdfe7e"/>
-    <ds:schemaRef ds:uri="2d3c347e-deae-4f57-8eaf-3772dd4433c8"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F143D2EB-8BE1-46FD-AA36-F0A52D61EC19}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -911,4 +892,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D39C44C-96D4-4F11-B752-6A8BD1FE27AD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9a016a34-9640-43fb-86ea-5daabefdfe7e"/>
+    <ds:schemaRef ds:uri="2d3c347e-deae-4f57-8eaf-3772dd4433c8"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26368CF4-F3C0-43C6-B5BF-C4E959C1D0AC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/tool/package-generator/clients/地域共催.xlsx
+++ b/tool/package-generator/clients/地域共催.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\package-generator\clients\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F22922CC-DCE5-4136-AE24-F7DE664A08A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40892CA5-49FB-4A16-9D26-C784DBB6BB16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -661,6 +661,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9a016a34-9640-43fb-86ea-5daabefdfe7e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="2d3c347e-deae-4f57-8eaf-3772dd4433c8" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101003F084FCF046B4A45A11E77E3180ECC70" ma:contentTypeVersion="11" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="93b3c00843758588d82b9b1cc445674f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9a016a34-9640-43fb-86ea-5daabefdfe7e" xmlns:ns3="2d3c347e-deae-4f57-8eaf-3772dd4433c8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3ba47e2a8c0ba124aa1c5a854c46141a" ns2:_="" ns3:_="">
     <xsd:import namespace="9a016a34-9640-43fb-86ea-5daabefdfe7e"/>
@@ -855,27 +875,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9a016a34-9640-43fb-86ea-5daabefdfe7e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="2d3c347e-deae-4f57-8eaf-3772dd4433c8" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26368CF4-F3C0-43C6-B5BF-C4E959C1D0AC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D39C44C-96D4-4F11-B752-6A8BD1FE27AD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9a016a34-9640-43fb-86ea-5daabefdfe7e"/>
+    <ds:schemaRef ds:uri="2d3c347e-deae-4f57-8eaf-3772dd4433c8"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F143D2EB-8BE1-46FD-AA36-F0A52D61EC19}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -892,23 +911,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D39C44C-96D4-4F11-B752-6A8BD1FE27AD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="9a016a34-9640-43fb-86ea-5daabefdfe7e"/>
-    <ds:schemaRef ds:uri="2d3c347e-deae-4f57-8eaf-3772dd4433c8"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26368CF4-F3C0-43C6-B5BF-C4E959C1D0AC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/tool/package-generator/clients/地域共催.xlsx
+++ b/tool/package-generator/clients/地域共催.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\package-generator\clients\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40892CA5-49FB-4A16-9D26-C784DBB6BB16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C88A2C88-923A-4C07-AA63-6BE9E6F4CF4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -661,26 +661,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9a016a34-9640-43fb-86ea-5daabefdfe7e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="2d3c347e-deae-4f57-8eaf-3772dd4433c8" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101003F084FCF046B4A45A11E77E3180ECC70" ma:contentTypeVersion="11" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="93b3c00843758588d82b9b1cc445674f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9a016a34-9640-43fb-86ea-5daabefdfe7e" xmlns:ns3="2d3c347e-deae-4f57-8eaf-3772dd4433c8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3ba47e2a8c0ba124aa1c5a854c46141a" ns2:_="" ns3:_="">
     <xsd:import namespace="9a016a34-9640-43fb-86ea-5daabefdfe7e"/>
@@ -875,26 +855,27 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9a016a34-9640-43fb-86ea-5daabefdfe7e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="2d3c347e-deae-4f57-8eaf-3772dd4433c8" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26368CF4-F3C0-43C6-B5BF-C4E959C1D0AC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D39C44C-96D4-4F11-B752-6A8BD1FE27AD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="9a016a34-9640-43fb-86ea-5daabefdfe7e"/>
-    <ds:schemaRef ds:uri="2d3c347e-deae-4f57-8eaf-3772dd4433c8"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F143D2EB-8BE1-46FD-AA36-F0A52D61EC19}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -911,4 +892,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D39C44C-96D4-4F11-B752-6A8BD1FE27AD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9a016a34-9640-43fb-86ea-5daabefdfe7e"/>
+    <ds:schemaRef ds:uri="2d3c347e-deae-4f57-8eaf-3772dd4433c8"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26368CF4-F3C0-43C6-B5BF-C4E959C1D0AC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/tool/package-generator/clients/地域共催.xlsx
+++ b/tool/package-generator/clients/地域共催.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\package-generator\clients\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C88A2C88-923A-4C07-AA63-6BE9E6F4CF4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80280756-6C05-44E4-99AB-9842CDD62B82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -661,6 +661,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9a016a34-9640-43fb-86ea-5daabefdfe7e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="2d3c347e-deae-4f57-8eaf-3772dd4433c8" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101003F084FCF046B4A45A11E77E3180ECC70" ma:contentTypeVersion="11" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="93b3c00843758588d82b9b1cc445674f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9a016a34-9640-43fb-86ea-5daabefdfe7e" xmlns:ns3="2d3c347e-deae-4f57-8eaf-3772dd4433c8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3ba47e2a8c0ba124aa1c5a854c46141a" ns2:_="" ns3:_="">
     <xsd:import namespace="9a016a34-9640-43fb-86ea-5daabefdfe7e"/>
@@ -855,27 +875,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9a016a34-9640-43fb-86ea-5daabefdfe7e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="2d3c347e-deae-4f57-8eaf-3772dd4433c8" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26368CF4-F3C0-43C6-B5BF-C4E959C1D0AC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D39C44C-96D4-4F11-B752-6A8BD1FE27AD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9a016a34-9640-43fb-86ea-5daabefdfe7e"/>
+    <ds:schemaRef ds:uri="2d3c347e-deae-4f57-8eaf-3772dd4433c8"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F143D2EB-8BE1-46FD-AA36-F0A52D61EC19}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -892,23 +911,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D39C44C-96D4-4F11-B752-6A8BD1FE27AD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="9a016a34-9640-43fb-86ea-5daabefdfe7e"/>
-    <ds:schemaRef ds:uri="2d3c347e-deae-4f57-8eaf-3772dd4433c8"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26368CF4-F3C0-43C6-B5BF-C4E959C1D0AC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/tool/package-generator/clients/地域共催.xlsx
+++ b/tool/package-generator/clients/地域共催.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\package-generator\clients\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80280756-6C05-44E4-99AB-9842CDD62B82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AAD8230-3128-4970-B405-5416D29D9874}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
